--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484345_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484345_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1826</v>
+        <v>4.8478</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3924</v>
+        <v>4.5946</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2098</v>
+        <v>0.2532</v>
       </c>
       <c r="G2" t="n">
         <v>7.0181</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1276</v>
+        <v>-0.4624</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5447</v>
+        <v>-0.3425</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5829</v>
+        <v>-0.1199</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7312</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1779</v>
+        <v>3.6525</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2539</v>
+        <v>3.4561</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.076</v>
+        <v>0.1964</v>
       </c>
       <c r="G3" t="n">
         <v>2.9781</v>
@@ -688,13 +688,13 @@
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7016</v>
+        <v>-0.2271</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3026</v>
+        <v>-0.1004</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.399</v>
+        <v>-0.1267</v>
       </c>
       <c r="V3" t="n">
         <v>1.0968</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8656</v>
+        <v>2.5283</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3514</v>
+        <v>0.7632</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5142</v>
+        <v>1.7652</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8516</v>
+        <v>3.3761</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5669</v>
+        <v>3.3899</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7154</v>
+        <v>-0.0138</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9746</v>
+        <v>3.3218</v>
       </c>
       <c r="K4" t="n">
-        <v>4.34</v>
+        <v>2.6605</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6613</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.123</v>
+        <v>0.0543</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7731</v>
+        <v>0.7294</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.35</v>
+        <v>-0.6751</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.586</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7768</v>
+        <v>-0.3399</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0522</v>
+        <v>-0.6052</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8289</v>
+        <v>0.2654</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1767</v>
+        <v>0.6642</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7312</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4406</v>
+        <v>1.8542</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7026</v>
+        <v>2.0481</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7379</v>
+        <v>-0.1939</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3761</v>
+        <v>2.8516</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3899</v>
+        <v>3.5669</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0138</v>
+        <v>-0.7154</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3218</v>
+        <v>4.9746</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6605</v>
+        <v>4.34</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6613</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0543</v>
+        <v>-2.123</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7294</v>
+        <v>-0.7731</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6751</v>
+        <v>-1.35</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-3.1255</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4276</v>
+        <v>-0.2347</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6657</v>
+        <v>-0.3555</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2381</v>
+        <v>0.1208</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6642</v>
+        <v>-0.1767</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6642</v>
+        <v>-0.7312</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2336</v>
+        <v>0.4575</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9065</v>
+        <v>0.967</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6728</v>
+        <v>-0.5094</v>
       </c>
       <c r="G6" t="n">
         <v>0.1714</v>
@@ -922,13 +922,13 @@
         <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5238</v>
+        <v>-0.2999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4237</v>
+        <v>-0.3631</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1002</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1508</v>
+        <v>-0.7729</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6068</v>
+        <v>-0.8496</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7575</v>
+        <v>0.0766</v>
       </c>
       <c r="G7" t="n">
         <v>3.0288</v>
@@ -1000,13 +1000,13 @@
         <v>2.1488</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6698</v>
+        <v>0.7461</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1294</v>
+        <v>-0.1134</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5404</v>
+        <v>0.8595</v>
       </c>
       <c r="V7" t="n">
         <v>-1.6177</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5643</v>
+        <v>-1.1497</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3426</v>
+        <v>-0.2821</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2217</v>
+        <v>-0.8676</v>
       </c>
       <c r="G8" t="n">
         <v>0.5745</v>
@@ -1078,13 +1078,13 @@
         <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.4004</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6657</v>
+        <v>-0.6052</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1492</v>
+        <v>0.2048</v>
       </c>
       <c r="V8" t="n">
         <v>-2.1052</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9829</v>
+        <v>-1.6112</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4308</v>
+        <v>-3.168</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4478</v>
+        <v>1.5568</v>
       </c>
       <c r="G9" t="n">
         <v>2.3884</v>
@@ -1156,13 +1156,13 @@
         <v>2.7348</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8189</v>
+        <v>-0.4472</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9684</v>
+        <v>-0.7056</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1494</v>
+        <v>0.2584</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2316</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>9.5039</v>
+        <v>9.8065</v>
       </c>
       <c r="E10" t="n">
-        <v>7.2266</v>
+        <v>7.529299999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2771</v>
+        <v>2.2773</v>
       </c>
       <c r="G10" t="n">
         <v>22.387</v>
@@ -1234,10 +1234,10 @@
         <v>13.6741</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9679</v>
+        <v>-1.6655</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.4936</v>
+        <v>-3.1909</v>
       </c>
       <c r="U10" t="n">
         <v>1.5255</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.6673</v>
+        <v>3.2393</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4847</v>
+        <v>3.3835</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1826</v>
+        <v>-0.1442</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1368</v>
@@ -1312,13 +1312,13 @@
         <v>2.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8469</v>
+        <v>0.419</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1457</v>
+        <v>-0.2468</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9926</v>
+        <v>0.6657</v>
       </c>
       <c r="V11" t="n">
         <v>0.2224</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3002</v>
+        <v>1.2695</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6508</v>
+        <v>0.7592</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3506</v>
+        <v>0.5104</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7019</v>
+        <v>1.5405</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.5935</v>
+        <v>1.4193</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.1212</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7127</v>
+        <v>2.0247</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.449</v>
+        <v>1.9033</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1617</v>
+        <v>0.1214</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.4146</v>
+        <v>-0.4842</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.1446</v>
+        <v>-0.484</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.27</v>
+        <v>-0.0002</v>
       </c>
       <c r="P12" t="n">
-        <v>2.9301</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1255</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4078</v>
+        <v>0.1197</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0851</v>
+        <v>-0.2888</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4929</v>
+        <v>0.4085</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2423</v>
+        <v>1.1834</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7592</v>
+        <v>1.7519</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4831</v>
+        <v>-0.5685</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5405</v>
+        <v>-2.7019</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4193</v>
+        <v>-3.5935</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1212</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0247</v>
+        <v>0.7127</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9033</v>
+        <v>-0.449</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1214</v>
+        <v>1.1617</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4842</v>
+        <v>-3.4146</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.484</v>
+        <v>-3.1446</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0002</v>
+        <v>-0.27</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3907</v>
+        <v>2.9301</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R13" t="n">
-        <v>0.586</v>
+        <v>3.1255</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0925</v>
+        <v>0.291</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2888</v>
+        <v>0.016</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3813</v>
+        <v>0.2751</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1847</v>
+        <v>0.0553</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3167</v>
+        <v>0.6009</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.132</v>
+        <v>-0.5456</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.8591</v>
+        <v>-1.8197</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.5452</v>
+        <v>-0.8777</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6861</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8626</v>
+        <v>0.5115</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.3075</v>
+        <v>1.4531</v>
       </c>
       <c r="L14" t="n">
-        <v>3.1701</v>
+        <v>-0.9416</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.7217</v>
+        <v>-2.3312</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2377</v>
+        <v>-2.3308</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.484</v>
+        <v>-0.0004</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8717</v>
+        <v>0.2889</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4541</v>
+        <v>-0.1526</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4176</v>
+        <v>0.4415</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="15">
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5786</v>
+        <v>-0.3403</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0058</v>
+        <v>0.71</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5728</v>
+        <v>-1.0503</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8197</v>
+        <v>-1.8591</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8777</v>
+        <v>-3.5452</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9419999999999999</v>
+        <v>1.6861</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5115</v>
+        <v>0.8626</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4531</v>
+        <v>-2.3075</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.9416</v>
+        <v>3.1701</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3312</v>
+        <v>-2.7217</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.3308</v>
+        <v>-1.2377</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0004</v>
+        <v>-1.484</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.345</v>
+        <v>0.3468</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7592</v>
+        <v>-0.1526</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4143</v>
+        <v>0.4993</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-1.1055</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7789</v>
+        <v>-1.3693</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7159</v>
+        <v>0.2638</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3461</v>
+        <v>-0.6392</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.537</v>
+        <v>-0.5851</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8091</v>
+        <v>-0.0541</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6357</v>
+        <v>-0.2248</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3098</v>
+        <v>-0.3057</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6741</v>
+        <v>0.0809</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9818</v>
+        <v>-0.4144</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8468</v>
+        <v>-0.2793</v>
       </c>
       <c r="O17" t="n">
         <v>-0.135</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1822</v>
+        <v>0.1197</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1432</v>
+        <v>-0.1678</v>
       </c>
       <c r="U17" t="n">
-        <v>0.039</v>
+        <v>0.2875</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0696</v>
+        <v>-1.2209</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8557</v>
+        <v>0.5766</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.214</v>
+        <v>-1.7976</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7575</v>
+        <v>-1.3461</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7575</v>
+        <v>-0.537</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-0.8091</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3482</v>
+        <v>0.6357</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3482</v>
+        <v>1.3098</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.6741</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4093</v>
+        <v>-1.9818</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4093</v>
+        <v>-1.8468</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.135</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4925</v>
+        <v>-0.1017</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4925</v>
+        <v>-0.0591</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.0427</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>M. LLUCIÀ MONSÓ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2417</v>
+        <v>-1.2719</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3693</v>
+        <v>-1.0579</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1276</v>
+        <v>-0.214</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6392</v>
+        <v>-1.7575</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5851</v>
+        <v>-1.7575</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0541</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2248</v>
+        <v>-1.3482</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3057</v>
+        <v>-1.3482</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4144</v>
+        <v>-0.4093</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2793</v>
+        <v>-0.4093</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.135</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0165</v>
+        <v>0.2903</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1678</v>
+        <v>0.2903</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1513</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8609</v>
+        <v>-3.4068</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6145</v>
+        <v>-0.5819</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2464</v>
+        <v>-2.8249</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.404</v>
+        <v>-3.6505</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.1515</v>
+        <v>-4.447</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2525</v>
+        <v>0.7965</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6307</v>
+        <v>2.0016</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2724</v>
+        <v>-0.5488</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9031</v>
+        <v>2.5503</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.7733</v>
+        <v>-5.652</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.4239</v>
+        <v>-3.8982</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3494</v>
+        <v>-1.7538</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.0789</v>
+        <v>-3.1255</v>
       </c>
       <c r="R20" t="n">
         <v>3.9069</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2779</v>
+        <v>-0.5377</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6578000000000001</v>
+        <v>-0.6766</v>
       </c>
       <c r="U20" t="n">
-        <v>0.62</v>
+        <v>0.1389</v>
       </c>
       <c r="V20" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4373</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4609</v>
+        <v>-3.697</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3908</v>
+        <v>-3.4234</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.07</v>
+        <v>-0.2736</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6505</v>
+        <v>-5.404</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.447</v>
+        <v>-3.1515</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7965</v>
+        <v>-2.2525</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0016</v>
+        <v>-0.6307</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5488</v>
+        <v>0.2724</v>
       </c>
       <c r="L21" t="n">
-        <v>2.5503</v>
+        <v>-0.9031</v>
       </c>
       <c r="M21" t="n">
-        <v>-5.652</v>
+        <v>-4.7733</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.8982</v>
+        <v>-3.4239</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7538</v>
+        <v>-1.3494</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1255</v>
+        <v>-5.0789</v>
       </c>
       <c r="R21" t="n">
         <v>3.9069</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5917</v>
+        <v>0.4417</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4855</v>
+        <v>-0.1511</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1062</v>
+        <v>0.5928</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>2.4373</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6146</v>
+        <v>-4.074</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9709</v>
+        <v>-3.5664</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6438</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-4.343</v>
@@ -2170,13 +2170,13 @@
         <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1897</v>
+        <v>0.3509</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2805</v>
+        <v>0.124</v>
       </c>
       <c r="U22" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.227</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2772</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.503799999999998</v>
+        <v>-9.5039</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.277199999999999</v>
+        <v>-2.277299999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.226699999999999</v>
+        <v>-7.226599999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-22.3871</v>
@@ -2239,7 +2239,7 @@
         <v>-8.77</v>
       </c>
       <c r="P23" t="n">
-        <v>7.813599999999997</v>
+        <v>7.813599999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.6739</v>
@@ -2251,7 +2251,7 @@
         <v>1.9681</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.5255</v>
+        <v>-1.5256</v>
       </c>
       <c r="U23" t="n">
         <v>3.4936</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484345_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484345_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8478</v>
+        <v>5.8048</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5946</v>
+        <v>5.8048</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2532</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0181</v>
+        <v>5.8048</v>
       </c>
       <c r="H2" t="n">
-        <v>5.9673</v>
+        <v>3.3768</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0507</v>
+        <v>2.4279</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4532</v>
+        <v>5.8048</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9965</v>
+        <v>3.3768</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4568</v>
+        <v>2.4279</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4352</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0291</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.406</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4624</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3425</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1199</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.7312</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ MANZANARES</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +653,78 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6525</v>
+        <v>4.8478</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4561</v>
+        <v>4.5946</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1964</v>
+        <v>0.2532</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9781</v>
+        <v>7.0181</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1428</v>
+        <v>5.9673</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8354</v>
+        <v>1.0507</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4866</v>
+        <v>7.4532</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1108</v>
+        <v>5.9965</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3758</v>
+        <v>1.4568</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5085</v>
+        <v>-0.4352</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.968</v>
+        <v>-0.0291</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5405</v>
+        <v>-0.406</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2271</v>
+        <v>-0.4624</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1004</v>
+        <v>-0.3425</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1267</v>
+        <v>-0.1199</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0968</v>
+        <v>-0.7312</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1219</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MENENDEZ PEREZ</t>
+          <t>J. FERNANDEZ MANZANARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5283</v>
+        <v>3.6525</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7632</v>
+        <v>3.4561</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7652</v>
+        <v>0.1964</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3761</v>
+        <v>2.9781</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3899</v>
+        <v>2.1428</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0138</v>
+        <v>0.8354</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3218</v>
+        <v>4.4866</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6605</v>
+        <v>3.1108</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6613</v>
+        <v>1.3758</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0543</v>
+        <v>-1.5085</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7294</v>
+        <v>-0.968</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6751</v>
+        <v>-0.5405</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3399</v>
+        <v>-0.2271</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6052</v>
+        <v>-0.1004</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2654</v>
+        <v>-0.1267</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6642</v>
+        <v>1.0968</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6642</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PORTALEZ MUR</t>
+          <t>S. MENENDEZ PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8542</v>
+        <v>2.5283</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0481</v>
+        <v>0.7632</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1939</v>
+        <v>1.7652</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8516</v>
+        <v>3.3761</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5669</v>
+        <v>3.3899</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7154</v>
+        <v>-0.0138</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9746</v>
+        <v>3.3218</v>
       </c>
       <c r="K5" t="n">
-        <v>4.34</v>
+        <v>2.6605</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6613</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.123</v>
+        <v>0.0543</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7731</v>
+        <v>0.7294</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.35</v>
+        <v>-0.6751</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.586</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2347</v>
+        <v>-0.3399</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3555</v>
+        <v>-0.6052</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1208</v>
+        <v>0.2654</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1767</v>
+        <v>0.6642</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7312</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>M. PORTALEZ MUR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4575</v>
+        <v>1.8542</v>
       </c>
       <c r="E6" t="n">
-        <v>0.967</v>
+        <v>2.0481</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5094</v>
+        <v>-0.1939</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1714</v>
+        <v>2.8516</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0558</v>
+        <v>3.5669</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2272</v>
+        <v>-0.7154</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3301</v>
+        <v>4.9746</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5718</v>
+        <v>4.34</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9019</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1587</v>
+        <v>-2.123</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.484</v>
+        <v>-0.7731</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6747</v>
+        <v>-1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>-0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2999</v>
+        <v>-0.2347</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3631</v>
+        <v>-0.3555</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.1208</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1767</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.7312</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7729</v>
+        <v>0.4575</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8496</v>
+        <v>0.967</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0766</v>
+        <v>-0.5094</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0288</v>
+        <v>0.1714</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3863</v>
+        <v>-1.0558</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6425</v>
+        <v>1.2272</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3427</v>
+        <v>1.3301</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0246</v>
+        <v>-0.5718</v>
       </c>
       <c r="L7" t="n">
-        <v>3.3182</v>
+        <v>1.9019</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3139</v>
+        <v>-1.1587</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6382</v>
+        <v>-0.484</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6757</v>
+        <v>-0.6747</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.9301</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.0789</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7461</v>
+        <v>-0.2999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1134</v>
+        <v>-0.3631</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8595</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.6177</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6177</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. CLEDJO HOUNGUES</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1497</v>
+        <v>-0.7729</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2821</v>
+        <v>-0.8496</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8676</v>
+        <v>0.0766</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5745</v>
+        <v>3.0288</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2067</v>
+        <v>0.3863</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6322</v>
+        <v>2.6425</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0459</v>
+        <v>4.3427</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2727</v>
+        <v>1.0246</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2268</v>
+        <v>3.3182</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5286</v>
+        <v>-1.3139</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9340000000000001</v>
+        <v>-0.6382</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4054</v>
+        <v>-0.6757</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7814</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.0789</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4004</v>
+        <v>0.7461</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6052</v>
+        <v>-0.1134</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2048</v>
+        <v>0.8595</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1052</v>
+        <v>-1.6177</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.3824</v>
+        <v>-1.6177</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>N. CLEDJO HOUNGUES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6112</v>
+        <v>-1.1497</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.168</v>
+        <v>-0.2821</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5568</v>
+        <v>-0.8676</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3884</v>
+        <v>0.5745</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0903</v>
+        <v>2.2067</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7019</v>
+        <v>-1.6322</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7029</v>
+        <v>0.0459</v>
       </c>
       <c r="K9" t="n">
-        <v>3.0545</v>
+        <v>1.2727</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6484</v>
+        <v>-1.2268</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3145</v>
+        <v>0.5286</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0359</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3504</v>
+        <v>-0.4054</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.3208</v>
+        <v>0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.0556</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7348</v>
+        <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4472</v>
+        <v>-0.4004</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7056</v>
+        <v>-0.6052</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2584</v>
+        <v>0.2048</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2316</v>
+        <v>-2.1052</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1097</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1219</v>
+        <v>-2.3824</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. DIAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,526 +1234,552 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>9.8065</v>
+        <v>-7.416</v>
       </c>
       <c r="E10" t="n">
-        <v>7.529299999999998</v>
+        <v>-8.972799999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2773</v>
+        <v>1.5568</v>
       </c>
       <c r="G10" t="n">
-        <v>22.387</v>
+        <v>-3.4164</v>
       </c>
       <c r="H10" t="n">
-        <v>19.6944</v>
+        <v>-0.2865</v>
       </c>
       <c r="I10" t="n">
-        <v>2.692499999999999</v>
+        <v>-3.1299</v>
       </c>
       <c r="J10" t="n">
-        <v>29.6578</v>
+        <v>-2.1019</v>
       </c>
       <c r="K10" t="n">
-        <v>20.8878</v>
+        <v>-0.3224</v>
       </c>
       <c r="L10" t="n">
-        <v>8.770200000000001</v>
+        <v>-1.7795</v>
       </c>
       <c r="M10" t="n">
-        <v>-7.2709</v>
+        <v>-1.3145</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1931</v>
+        <v>0.0359</v>
       </c>
       <c r="O10" t="n">
-        <v>-6.0778</v>
+        <v>-1.3504</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.813599999999999</v>
+        <v>-3.3208</v>
       </c>
       <c r="Q10" t="n">
-        <v>-21.4877</v>
+        <v>-6.0556</v>
       </c>
       <c r="R10" t="n">
-        <v>13.6741</v>
+        <v>2.7348</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6655</v>
+        <v>-0.4472</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.1909</v>
+        <v>-0.7056</v>
       </c>
       <c r="U10" t="n">
-        <v>1.5255</v>
+        <v>0.2584</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.101399999999999</v>
+        <v>-0.2316</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5499</v>
+        <v>-0.1097</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.6514</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>C.B. CUARTE DE HUERVA</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.2393</v>
+        <v>9.806499999999996</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3835</v>
+        <v>7.529299999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1442</v>
+        <v>2.2773</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1368</v>
+        <v>22.387</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1867</v>
+        <v>19.6944</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3235</v>
+        <v>2.6924</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6033</v>
+        <v>29.6578</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1732</v>
+        <v>20.8877</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4301</v>
+        <v>8.770200000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.7401</v>
+        <v>-7.2709</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9864</v>
+        <v>-1.1931</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7536</v>
+        <v>-6.0778</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7348</v>
+        <v>-7.8136</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1953</v>
+        <v>-21.4877</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9301</v>
+        <v>13.6741</v>
       </c>
       <c r="S11" t="n">
-        <v>0.419</v>
+        <v>-1.6655</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2468</v>
+        <v>-3.1909</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6657</v>
+        <v>1.5255</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2224</v>
+        <v>-3.101399999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2224</v>
+        <v>2.5499</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
-      </c>
+        <v>-5.651400000000001</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2695</v>
+        <v>3.2393</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7592</v>
+        <v>3.3835</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5104</v>
+        <v>-0.1442</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5405</v>
+        <v>-0.1368</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4193</v>
+        <v>0.1867</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1212</v>
+        <v>-0.3235</v>
       </c>
       <c r="J12" t="n">
-        <v>2.0247</v>
+        <v>3.6033</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9033</v>
+        <v>2.1732</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1214</v>
+        <v>1.4301</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4842</v>
+        <v>-3.7401</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.484</v>
+        <v>-1.9864</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0002</v>
+        <v>-1.7536</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3907</v>
+        <v>2.7348</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>2.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1197</v>
+        <v>0.419</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2888</v>
+        <v>-0.2468</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4085</v>
+        <v>0.6657</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2224</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1834</v>
+        <v>2.1279</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7519</v>
+        <v>2.1279</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5685</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.7019</v>
+        <v>2.1279</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.5935</v>
+        <v>0.307</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8915999999999999</v>
+        <v>1.821</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7127</v>
+        <v>2.1279</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.449</v>
+        <v>0.307</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1617</v>
+        <v>1.821</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.4146</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.1446</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1255</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.291</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2751</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0553</v>
+        <v>1.2695</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6009</v>
+        <v>0.7592</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5456</v>
+        <v>0.5104</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.8197</v>
+        <v>1.5405</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8777</v>
+        <v>1.4193</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9419999999999999</v>
+        <v>0.1212</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5115</v>
+        <v>2.0247</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4531</v>
+        <v>1.9033</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.9416</v>
+        <v>0.1214</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3312</v>
+        <v>-0.4842</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.3308</v>
+        <v>-0.484</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0004</v>
+        <v>-0.0002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2889</v>
+        <v>0.1197</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1526</v>
+        <v>-0.2888</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4415</v>
+        <v>0.4085</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. SUÑOL CUBARSI</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.135</v>
+        <v>1.1834</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0605</v>
+        <v>1.7519</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0745</v>
+        <v>-0.5685</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2698</v>
+        <v>-2.7019</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-3.5935</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2698</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7127</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0.449</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.1617</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2698</v>
+        <v>-3.4146</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-3.1446</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2698</v>
+        <v>-0.27</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>2.9301</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1953</v>
+        <v>3.1255</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0605</v>
+        <v>0.291</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0605</v>
+        <v>0.016</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.2751</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3403</v>
+        <v>0.921</v>
       </c>
       <c r="E16" t="n">
-        <v>0.71</v>
+        <v>0.921</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0503</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8591</v>
+        <v>0.921</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.5452</v>
+        <v>0.921</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6861</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8626</v>
+        <v>0.921</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.3075</v>
+        <v>0.921</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1701</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.7217</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2377</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.484</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3468</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1526</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4993</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1718,231 +1789,246 @@
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1055</v>
+        <v>0.0553</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3693</v>
+        <v>0.6009</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2638</v>
+        <v>-0.5456</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6392</v>
+        <v>-1.8197</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5851</v>
+        <v>-0.8777</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0541</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2248</v>
+        <v>0.5115</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3057</v>
+        <v>1.4531</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0809</v>
+        <v>-0.9416</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4144</v>
+        <v>-2.3312</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2793</v>
+        <v>-2.3308</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.135</v>
+        <v>-0.0004</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1197</v>
+        <v>0.2889</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1678</v>
+        <v>-0.1526</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2875</v>
+        <v>0.4415</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>P. SUNOL CUBARSI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2209</v>
+        <v>-0.135</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5766</v>
+        <v>-0.0605</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7976</v>
+        <v>-0.0745</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3461</v>
+        <v>-0.2698</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.537</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8091</v>
+        <v>-0.2698</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6357</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3098</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9818</v>
+        <v>-0.2698</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8468</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.135</v>
+        <v>-0.2698</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1017</v>
+        <v>-0.0605</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0591</v>
+        <v>-0.0605</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0427</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2719</v>
+        <v>-0.3403</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0579</v>
+        <v>0.71</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.214</v>
+        <v>-1.0503</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7575</v>
+        <v>-1.8591</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7575</v>
+        <v>-3.5452</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1.6861</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3482</v>
+        <v>0.8626</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3482</v>
+        <v>-2.3075</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.1701</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4093</v>
+        <v>-2.7217</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4093</v>
+        <v>-1.2377</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.484</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2903</v>
+        <v>0.3468</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2903</v>
+        <v>-0.1526</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.4993</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,319 +2038,589 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4068</v>
+        <v>-1.1055</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5819</v>
+        <v>-1.3693</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8249</v>
+        <v>0.2638</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6505</v>
+        <v>-0.6392</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.447</v>
+        <v>-0.5851</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7965</v>
+        <v>-0.0541</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0016</v>
+        <v>-0.2248</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5488</v>
+        <v>-0.3057</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5503</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>-5.652</v>
+        <v>-0.4144</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.8982</v>
+        <v>-0.2793</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7538</v>
+        <v>-0.135</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1255</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>3.9069</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5377</v>
+        <v>0.1197</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6766</v>
+        <v>-0.1678</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1389</v>
+        <v>0.2875</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.697</v>
+        <v>-1.2209</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4234</v>
+        <v>0.5766</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2736</v>
+        <v>-1.7976</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.404</v>
+        <v>-1.3461</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.1515</v>
+        <v>-0.537</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2525</v>
+        <v>-0.8091</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6307</v>
+        <v>0.6357</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2724</v>
+        <v>1.3098</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9031</v>
+        <v>-0.6741</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.7733</v>
+        <v>-1.9818</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.4239</v>
+        <v>-1.8468</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3494</v>
+        <v>-0.135</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.0789</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.9069</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4417</v>
+        <v>-0.1017</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1511</v>
+        <v>-0.0591</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5928</v>
+        <v>-0.0427</v>
       </c>
       <c r="V21" t="n">
-        <v>2.4373</v>
+        <v>-0.5545</v>
       </c>
       <c r="W21" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>M. LLUCIA MONSO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.074</v>
+        <v>-1.2719</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5664</v>
+        <v>-1.0579</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.214</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.343</v>
+        <v>-1.7575</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.8061</v>
+        <v>-1.7575</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5369</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8774</v>
+        <v>-1.3482</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9594</v>
+        <v>-1.3482</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0819</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.4656</v>
+        <v>-0.4093</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8468</v>
+        <v>-0.4093</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6188</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3509</v>
+        <v>0.2903</v>
       </c>
       <c r="T22" t="n">
-        <v>0.124</v>
+        <v>0.2903</v>
       </c>
       <c r="U22" t="n">
-        <v>0.227</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.5039</v>
+        <v>-3.4068</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.277299999999999</v>
+        <v>-0.5819</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.226599999999999</v>
+        <v>-2.8249</v>
       </c>
       <c r="G23" t="n">
+        <v>-3.6505</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-4.447</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7965</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.0016</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.5488</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.5503</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-5.652</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-3.8982</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.7538</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.9069</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.5377</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.6766</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A. ABELLO GIRVES</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4.618</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-4.3444</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.2736</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-6.3249</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-4.0725</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-2.2525</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.5516</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.6486</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.9031</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-4.7733</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-3.4239</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.3494</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-5.0789</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.9069</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.1511</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2.4373</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.4373</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P. CARRION SORIANO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-6.2019</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-5.6943</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.5076000000000001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-6.471</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.1131</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-3.3579</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-3.0054</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.2663</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.739</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-3.4656</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.8468</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.6188</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484345_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-9.503900000000002</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2.277300000000001</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-7.2266</v>
+      </c>
+      <c r="G26" t="n">
         <v>-22.3871</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H26" t="n">
         <v>-19.6946</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I26" t="n">
         <v>-2.6925</v>
       </c>
-      <c r="J23" t="n">
-        <v>7.270999999999999</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1.1932</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6.077599999999999</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="J26" t="n">
+        <v>7.270999999999997</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.1933</v>
+      </c>
+      <c r="L26" t="n">
+        <v>6.077699999999999</v>
+      </c>
+      <c r="M26" t="n">
         <v>-29.658</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N26" t="n">
         <v>-20.8878</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O26" t="n">
         <v>-8.77</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P26" t="n">
         <v>7.813599999999999</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q26" t="n">
         <v>-13.6739</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>21.4877</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S26" t="n">
         <v>1.9681</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>-1.5256</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>3.4936</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>3.1015</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W26" t="n">
         <v>5.6513</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>-2.55</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
